--- a/data/Bootverhuur_Prices.xlsx
+++ b/data/Bootverhuur_Prices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capgemini-my.sharepoint.com/personal/rutger_ter_wee_capgemini_com/Documents/Documents/CapGemini/Projecten/Academy/Trainingen/IT Vitea/Bootjescasus/Deelnemers/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\regnorash\itvitae\java\molveno_reservations\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{B6753C7E-D844-4E2D-ACED-05E2F99B8C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F69506B-7DA6-47E6-9129-C2BCBAE224D4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F39F7C-D686-4052-A2AD-9C44F76E12DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
   <si>
     <t>Boat ID</t>
   </si>
@@ -110,6 +110,9 @@
   </si>
   <si>
     <t>1 person Kayak</t>
+  </si>
+  <si>
+    <t>B-06</t>
   </si>
 </sst>
 </file>
@@ -478,20 +481,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" customWidth="1"/>
-    <col min="4" max="4" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.21875" customWidth="1"/>
-    <col min="9" max="10" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.28515625" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,7 +526,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -555,7 +558,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -587,7 +590,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -619,7 +622,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -651,7 +654,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -683,9 +686,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
